--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mini\Documents\25\project\tree\222\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\i7\drevo\7\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27300" windowHeight="9585" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="6195"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="foto_family" sheetId="4" r:id="rId4"/>
     <sheet name="foto_group" sheetId="5" r:id="rId5"/>
     <sheet name="foto_location" sheetId="6" r:id="rId6"/>
-    <sheet name="event" sheetId="7" r:id="rId7"/>
-    <sheet name="language" sheetId="8" r:id="rId8"/>
-    <sheet name="help" sheetId="9" r:id="rId9"/>
+    <sheet name="foto_item" sheetId="10" r:id="rId7"/>
+    <sheet name="event" sheetId="7" r:id="rId8"/>
+    <sheet name="language" sheetId="8" r:id="rId9"/>
+    <sheet name="help" sheetId="9" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$22</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="359">
   <si>
     <t>idA</t>
   </si>
@@ -116,9 +117,6 @@
     <t>21.01.1924</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394</t>
-  </si>
-  <si>
     <t>Симбирск</t>
   </si>
   <si>
@@ -1101,6 +1099,15 @@
   </si>
   <si>
     <t>число детей:</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
+  </si>
+  <si>
+    <t>Ульянов</t>
+  </si>
+  <si>
+    <t>/md_person/Ульянин_Николай_Васильевич.md</t>
   </si>
 </sst>
 </file>
@@ -1501,6 +1508,10 @@
     <col min="12" max="12" width="16" style="7" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="7" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1546,19 +1557,19 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1595,19 +1606,19 @@
         <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1616,40 +1627,40 @@
         <v>Ульянов_Илья_Николаевич</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="O3" t="s">
         <v>38</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" t="s">
         <v>39</v>
-      </c>
-      <c r="P3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1658,43 +1669,43 @@
         <v>Бланк_Мария_Александровна</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" t="s">
         <v>44</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="O4" t="s">
         <v>48</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>49</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>50</v>
-      </c>
-      <c r="R4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1703,32 +1714,38 @@
         <v>Ульянин_Николай_Васильевич</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="D5" s="4" t="s">
+        <v>357</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="G5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="O5" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" t="s">
         <v>55</v>
-      </c>
-      <c r="P5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1737,31 +1754,31 @@
         <v>Смирнова_Анна_Алексеевна</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="O6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" t="s">
         <v>59</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1770,34 +1787,34 @@
         <v>Бланк_Александр_Дмитриевич</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
       </c>
       <c r="J7" t="s">
+        <v>343</v>
+      </c>
+      <c r="K7" t="s">
         <v>344</v>
       </c>
-      <c r="K7" t="s">
-        <v>345</v>
-      </c>
       <c r="O7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" t="s">
         <v>63</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>64</v>
-      </c>
-      <c r="R7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1806,31 +1823,31 @@
         <v>Гроссшопф_Анна_Ивановна</v>
       </c>
       <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" t="s">
         <v>67</v>
       </c>
-      <c r="I8" t="s">
+      <c r="O8" t="s">
         <v>68</v>
       </c>
-      <c r="J8" t="s">
-        <v>68</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>69</v>
       </c>
-      <c r="P8" t="s">
-        <v>70</v>
-      </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1839,13 +1856,13 @@
         <v>Ульянова_Анна_Ильинична</v>
       </c>
       <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
         <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
@@ -1854,19 +1871,19 @@
         <v>23</v>
       </c>
       <c r="G9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" t="s">
         <v>74</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>75</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>76</v>
-      </c>
-      <c r="K9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1875,7 +1892,7 @@
         <v>Ульянов_Александр_Ильич</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -1887,19 +1904,19 @@
         <v>23</v>
       </c>
       <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" t="s">
         <v>80</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>81</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>82</v>
-      </c>
-      <c r="K10" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1908,10 +1925,10 @@
         <v>Ульянова_Ольга_Ильинична</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
@@ -1920,19 +1937,19 @@
         <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" t="s">
         <v>85</v>
-      </c>
-      <c r="J11" t="s">
-        <v>85</v>
-      </c>
-      <c r="K11" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1941,7 +1958,7 @@
         <v>Ульянов_Дмитрий_Ильич</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -1953,19 +1970,19 @@
         <v>23</v>
       </c>
       <c r="G12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="J12" t="s">
         <v>88</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>89</v>
-      </c>
-      <c r="J12" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1974,10 +1991,10 @@
         <v>Ульянова_Мария_Ильинична</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
@@ -1986,19 +2003,19 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" t="s">
         <v>93</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>94</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>95</v>
-      </c>
-      <c r="K13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -2007,25 +2024,25 @@
         <v>Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" t="s">
         <v>97</v>
       </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" t="s">
         <v>99</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>100</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>101</v>
-      </c>
-      <c r="K14" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -2034,31 +2051,31 @@
         <v>Ульянов_Василий_Николаевич</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
       <c r="G15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" t="s">
         <v>105</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R15" t="s">
         <v>106</v>
-      </c>
-      <c r="J15" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2067,34 +2084,34 @@
         <v>Ульянова_Мария_Николаевна</v>
       </c>
       <c r="B16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
         <v>108</v>
       </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
         <v>109</v>
       </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" t="s">
-        <v>110</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2103,28 +2120,28 @@
         <v>Ульянова_Феодосия_Николаевна</v>
       </c>
       <c r="B17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" t="s">
         <v>111</v>
       </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="J17" t="s">
         <v>112</v>
-      </c>
-      <c r="I17" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -2133,37 +2150,37 @@
         <v>Бланк_Дмитрий_Александрович</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
         <v>44</v>
       </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
       <c r="G18" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" t="s">
         <v>116</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>117</v>
       </c>
-      <c r="J18" t="s">
+      <c r="O18" t="s">
         <v>118</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>119</v>
       </c>
-      <c r="P18" t="s">
+      <c r="R18" t="s">
         <v>120</v>
-      </c>
-      <c r="R18" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2172,34 +2189,34 @@
         <v>Бланк_Анна_Александровна</v>
       </c>
       <c r="B19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
         <v>122</v>
       </c>
-      <c r="C19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="I19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2208,34 +2225,34 @@
         <v>Бланк_Любовь_Александровна</v>
       </c>
       <c r="B20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
         <v>125</v>
       </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
         <v>126</v>
       </c>
-      <c r="E20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="I20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2244,34 +2261,34 @@
         <v>Бланк_Екатерина_Александровна</v>
       </c>
       <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" t="s">
         <v>129</v>
       </c>
-      <c r="C21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" t="s">
         <v>130</v>
       </c>
-      <c r="E21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="I21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2280,34 +2297,34 @@
         <v>Бланк_Софья_Александровна</v>
       </c>
       <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
         <v>133</v>
       </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E22" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="I22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2316,16 +2333,16 @@
         <v>Эссен_Екатерина_Ивановна</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I23" s="4">
         <v>1863</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2340,6 +2357,1173 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C107"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20" style="7" customWidth="1"/>
+    <col min="3" max="3" width="60" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>226</v>
+      </c>
+      <c r="B33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>196</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>197</v>
+      </c>
+      <c r="B51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>197</v>
+      </c>
+      <c r="B54" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>197</v>
+      </c>
+      <c r="B55" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>197</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>197</v>
+      </c>
+      <c r="B59" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>198</v>
+      </c>
+      <c r="B65" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>198</v>
+      </c>
+      <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>198</v>
+      </c>
+      <c r="B68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>198</v>
+      </c>
+      <c r="B69" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>199</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>199</v>
+      </c>
+      <c r="B73" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" t="s">
+        <v>186</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" t="s">
+        <v>187</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>199</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>199</v>
+      </c>
+      <c r="B83" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>199</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>199</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>199</v>
+      </c>
+      <c r="B86" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>239</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>239</v>
+      </c>
+      <c r="B88" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>239</v>
+      </c>
+      <c r="B89" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>239</v>
+      </c>
+      <c r="B90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>239</v>
+      </c>
+      <c r="B91" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>239</v>
+      </c>
+      <c r="B92" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" t="s">
+        <v>159</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>239</v>
+      </c>
+      <c r="B94" t="s">
+        <v>160</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>239</v>
+      </c>
+      <c r="B95" t="s">
+        <v>170</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>239</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>239</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" t="s">
+        <v>196</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>239</v>
+      </c>
+      <c r="B99" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>239</v>
+      </c>
+      <c r="B100" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>239</v>
+      </c>
+      <c r="B101" t="s">
+        <v>199</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>336</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>336</v>
+      </c>
+      <c r="B103" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>336</v>
+      </c>
+      <c r="B104" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>336</v>
+      </c>
+      <c r="B105" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>336</v>
+      </c>
+      <c r="B106" t="s">
+        <v>212</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>336</v>
+      </c>
+      <c r="B107" t="s">
+        <v>213</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>342</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2363,22 +3547,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2387,13 +3571,13 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>143</v>
-      </c>
-      <c r="L1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2408,13 +3592,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J2" t="s">
         <v>145</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>146</v>
-      </c>
-      <c r="K2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2423,19 +3607,19 @@
         <v>Бланк_Александр_Дмитриевич__Гроссшопф_Анна_Ивановна</v>
       </c>
       <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K3" t="s">
         <v>148</v>
-      </c>
-      <c r="K3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2444,22 +3628,22 @@
         <v>Ульянов_Владимир_Ильич__Крупская_Надежда_Константиновна</v>
       </c>
       <c r="B4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" t="s">
         <v>150</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>151</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>152</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>153</v>
       </c>
-      <c r="J4" t="s">
-        <v>154</v>
-      </c>
       <c r="K4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2468,22 +3652,22 @@
         <v>Ульянин_Николай_Васильевич__Смирнова_Анна_Алексеевна</v>
       </c>
       <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2492,16 +3676,16 @@
         <v>Бланк_Александр_Дмитриевич__Эссен_Екатерина_Ивановна</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -2517,142 +3701,148 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="7" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="7" customWidth="1"/>
     <col min="3" max="3" width="15" style="7" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="11" style="7" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" style="7" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" style="7" customWidth="1"/>
+    <col min="4" max="5" width="34.7109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="11" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="7" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2">
         <v>1922</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1922.jpg</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" t="s">
         <v>164</v>
       </c>
-      <c r="I2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="6"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G25" s="4"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="6"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2682,37 +3872,37 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -2721,40 +3911,40 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B2">
         <v>1879</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна-1879.jpg</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4">
         <v>1879</v>
       </c>
       <c r="L2" t="s">
+        <v>174</v>
+      </c>
+      <c r="M2" t="s">
         <v>175</v>
       </c>
-      <c r="M2" t="s">
-        <v>176</v>
-      </c>
       <c r="N2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -2836,31 +4026,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>1</v>
@@ -2871,68 +4061,68 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2">
         <v>1918</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульянов_Владимир_Ильич-1918.jpg</v>
       </c>
       <c r="E2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" t="s">
         <v>177</v>
       </c>
-      <c r="F2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" t="s">
         <v>179</v>
       </c>
-      <c r="J2" t="s">
-        <v>180</v>
-      </c>
       <c r="K2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3">
         <v>1918</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D3" t="str">
         <f>A3&amp;"-"&amp;B3&amp;"."&amp;C3</f>
         <v>Свердлов_Яков_Михайлович-1918.jpg</v>
       </c>
       <c r="E3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" t="s">
         <v>182</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>183</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J3" t="s">
         <v>184</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="J3" t="s">
-        <v>185</v>
-      </c>
       <c r="K3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -3019,37 +4209,37 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1</v>
@@ -3058,41 +4248,41 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" t="s">
         <v>190</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>191</v>
-      </c>
-      <c r="C2" t="s">
-        <v>192</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
         <v>Ульяновск_ Ленина_70-2020хх.png</v>
       </c>
       <c r="E2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
         <v>193</v>
       </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>194</v>
-      </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L2" s="9"/>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3102,6 +4292,65 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3121,28 +4370,28 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -3151,60 +4400,60 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" t="s">
         <v>201</v>
       </c>
-      <c r="C2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I2" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>203</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>204</v>
-      </c>
-      <c r="M2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" t="s">
         <v>206</v>
       </c>
-      <c r="C3" t="s">
-        <v>207</v>
-      </c>
       <c r="E3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" t="s">
         <v>177</v>
-      </c>
-      <c r="F3" t="s">
-        <v>178</v>
       </c>
       <c r="G3" s="4"/>
       <c r="M3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N3" t="s">
         <v>208</v>
-      </c>
-      <c r="N3" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3273,7 +4522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3287,19 +4536,19 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3311,1972 +4560,805 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" t="s">
         <v>215</v>
-      </c>
-      <c r="B2" t="s">
-        <v>216</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" t="s">
         <v>217</v>
-      </c>
-      <c r="E2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
         <v>215</v>
-      </c>
-      <c r="B3" t="s">
-        <v>216</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" t="s">
         <v>219</v>
-      </c>
-      <c r="E3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" t="s">
         <v>215</v>
-      </c>
-      <c r="B4" t="s">
-        <v>216</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" t="s">
         <v>221</v>
-      </c>
-      <c r="E4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" t="s">
         <v>215</v>
-      </c>
-      <c r="B5" t="s">
-        <v>216</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" t="s">
         <v>223</v>
-      </c>
-      <c r="E5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" t="s">
         <v>215</v>
-      </c>
-      <c r="B6" t="s">
-        <v>216</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" t="s">
         <v>225</v>
-      </c>
-      <c r="E6" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" t="s">
         <v>227</v>
       </c>
-      <c r="C7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>228</v>
-      </c>
-      <c r="E7" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" t="s">
         <v>230</v>
-      </c>
-      <c r="E8" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E9" t="s">
         <v>232</v>
-      </c>
-      <c r="E9" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" t="s">
         <v>225</v>
-      </c>
-      <c r="E10" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" t="s">
         <v>234</v>
-      </c>
-      <c r="E11" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" t="s">
         <v>230</v>
-      </c>
-      <c r="E12" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
         <v>236</v>
-      </c>
-      <c r="E13" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" t="s">
         <v>232</v>
-      </c>
-      <c r="E14" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" t="s">
         <v>225</v>
-      </c>
-      <c r="E15" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" t="s">
         <v>234</v>
-      </c>
-      <c r="E16" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E17" t="s">
         <v>230</v>
-      </c>
-      <c r="E17" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D18" t="s">
+        <v>235</v>
+      </c>
+      <c r="E18" t="s">
         <v>236</v>
-      </c>
-      <c r="E18" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" t="s">
         <v>232</v>
-      </c>
-      <c r="E19" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" t="s">
         <v>225</v>
-      </c>
-      <c r="E20" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" t="s">
         <v>234</v>
-      </c>
-      <c r="E21" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" t="s">
         <v>230</v>
-      </c>
-      <c r="E22" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" t="s">
         <v>236</v>
-      </c>
-      <c r="E23" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>231</v>
+      </c>
+      <c r="E24" t="s">
         <v>232</v>
-      </c>
-      <c r="E24" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
         <v>225</v>
-      </c>
-      <c r="E25" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" t="s">
         <v>234</v>
-      </c>
-      <c r="E26" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E27" t="s">
         <v>230</v>
-      </c>
-      <c r="E27" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
         <v>236</v>
-      </c>
-      <c r="E28" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" t="s">
+        <v>231</v>
+      </c>
+      <c r="E29" t="s">
         <v>232</v>
-      </c>
-      <c r="E29" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
         <v>225</v>
-      </c>
-      <c r="E30" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D31" t="s">
+        <v>237</v>
+      </c>
+      <c r="E31" t="s">
         <v>238</v>
-      </c>
-      <c r="E31" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" t="s">
         <v>234</v>
-      </c>
-      <c r="E32" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" t="s">
         <v>230</v>
-      </c>
-      <c r="E33" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" t="s">
         <v>236</v>
-      </c>
-      <c r="E34" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
       <c r="D35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E35" t="s">
         <v>232</v>
-      </c>
-      <c r="E35" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" t="s">
         <v>225</v>
-      </c>
-      <c r="E36" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
         <v>215</v>
-      </c>
-      <c r="B39" t="s">
-        <v>216</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
         <v>242</v>
-      </c>
-      <c r="E39" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" t="s">
         <v>215</v>
-      </c>
-      <c r="B40" t="s">
-        <v>216</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
         <v>244</v>
-      </c>
-      <c r="E40" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
         <v>215</v>
-      </c>
-      <c r="B41" t="s">
-        <v>216</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
       </c>
       <c r="D41" t="s">
+        <v>245</v>
+      </c>
+      <c r="E41" t="s">
         <v>246</v>
-      </c>
-      <c r="E41" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" t="s">
         <v>215</v>
-      </c>
-      <c r="B42" t="s">
-        <v>216</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="s">
+        <v>247</v>
+      </c>
+      <c r="E42" t="s">
         <v>248</v>
-      </c>
-      <c r="E42" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D43" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E43" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E44" t="s">
         <v>251</v>
-      </c>
-      <c r="E44" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B45" t="s">
         <v>215</v>
-      </c>
-      <c r="B45" t="s">
-        <v>216</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
+        <v>252</v>
+      </c>
+      <c r="E45" t="s">
         <v>253</v>
-      </c>
-      <c r="E45" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D46" t="s">
+        <v>254</v>
+      </c>
+      <c r="E46" t="s">
         <v>255</v>
-      </c>
-      <c r="E46" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="20" style="7" customWidth="1"/>
-    <col min="3" max="3" width="60" style="7" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>216</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>216</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>216</v>
-      </c>
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>227</v>
-      </c>
-      <c r="B23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>227</v>
-      </c>
-      <c r="B24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>227</v>
-      </c>
-      <c r="B25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>227</v>
-      </c>
-      <c r="B26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>227</v>
-      </c>
-      <c r="B27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>227</v>
-      </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>227</v>
-      </c>
-      <c r="B29" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>227</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>227</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>227</v>
-      </c>
-      <c r="B33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>227</v>
-      </c>
-      <c r="B34" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>197</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>197</v>
-      </c>
-      <c r="B36" t="s">
-        <v>156</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>197</v>
-      </c>
-      <c r="B38" t="s">
-        <v>158</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>197</v>
-      </c>
-      <c r="B39" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>197</v>
-      </c>
-      <c r="B40" t="s">
-        <v>159</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>197</v>
-      </c>
-      <c r="B41" t="s">
-        <v>160</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B42" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>197</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>197</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>198</v>
-      </c>
-      <c r="B46" t="s">
-        <v>166</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" t="s">
-        <v>167</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>198</v>
-      </c>
-      <c r="B48" t="s">
-        <v>158</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>198</v>
-      </c>
-      <c r="B49" t="s">
-        <v>0</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>198</v>
-      </c>
-      <c r="B50" t="s">
-        <v>159</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>198</v>
-      </c>
-      <c r="B51" t="s">
-        <v>168</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>198</v>
-      </c>
-      <c r="B52" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>198</v>
-      </c>
-      <c r="B53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>198</v>
-      </c>
-      <c r="B54" t="s">
-        <v>160</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>198</v>
-      </c>
-      <c r="B55" t="s">
-        <v>161</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>198</v>
-      </c>
-      <c r="B56" t="s">
-        <v>171</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>198</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>198</v>
-      </c>
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>198</v>
-      </c>
-      <c r="B59" t="s">
-        <v>172</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>199</v>
-      </c>
-      <c r="B61" t="s">
-        <v>156</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" t="s">
-        <v>167</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>199</v>
-      </c>
-      <c r="B63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>199</v>
-      </c>
-      <c r="B64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>199</v>
-      </c>
-      <c r="B65" t="s">
-        <v>159</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" t="s">
-        <v>172</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>199</v>
-      </c>
-      <c r="B67" t="s">
-        <v>160</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>199</v>
-      </c>
-      <c r="B68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>199</v>
-      </c>
-      <c r="B69" t="s">
-        <v>171</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>199</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>199</v>
-      </c>
-      <c r="B71" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>200</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>200</v>
-      </c>
-      <c r="B73" t="s">
-        <v>186</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>200</v>
-      </c>
-      <c r="B74" t="s">
-        <v>157</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>200</v>
-      </c>
-      <c r="B75" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>200</v>
-      </c>
-      <c r="B76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>200</v>
-      </c>
-      <c r="B77" t="s">
-        <v>159</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>200</v>
-      </c>
-      <c r="B78" t="s">
-        <v>187</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>200</v>
-      </c>
-      <c r="B79" t="s">
-        <v>172</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>200</v>
-      </c>
-      <c r="B80" t="s">
-        <v>188</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>200</v>
-      </c>
-      <c r="B81" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>200</v>
-      </c>
-      <c r="B82" t="s">
-        <v>161</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>200</v>
-      </c>
-      <c r="B83" t="s">
-        <v>171</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>200</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>200</v>
-      </c>
-      <c r="B85" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>200</v>
-      </c>
-      <c r="B86" t="s">
-        <v>189</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>240</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>240</v>
-      </c>
-      <c r="B88" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>240</v>
-      </c>
-      <c r="B89" t="s">
-        <v>196</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>240</v>
-      </c>
-      <c r="B90" t="s">
-        <v>172</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>240</v>
-      </c>
-      <c r="B91" t="s">
-        <v>188</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>240</v>
-      </c>
-      <c r="B92" t="s">
-        <v>159</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>240</v>
-      </c>
-      <c r="B93" t="s">
-        <v>160</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>240</v>
-      </c>
-      <c r="B94" t="s">
-        <v>161</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>240</v>
-      </c>
-      <c r="B95" t="s">
-        <v>171</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>240</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>240</v>
-      </c>
-      <c r="B97" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>240</v>
-      </c>
-      <c r="B98" t="s">
-        <v>197</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>240</v>
-      </c>
-      <c r="B99" t="s">
-        <v>198</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>240</v>
-      </c>
-      <c r="B100" t="s">
-        <v>199</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>240</v>
-      </c>
-      <c r="B101" t="s">
-        <v>200</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>337</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>337</v>
-      </c>
-      <c r="B103" t="s">
-        <v>210</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>337</v>
-      </c>
-      <c r="B104" t="s">
-        <v>211</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>337</v>
-      </c>
-      <c r="B105" t="s">
-        <v>212</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>337</v>
-      </c>
-      <c r="B106" t="s">
-        <v>213</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>337</v>
-      </c>
-      <c r="B107" t="s">
-        <v>214</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>343</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="358">
   <si>
     <t>idA</t>
   </si>
@@ -1102,9 +1102,6 @@
   </si>
   <si>
     <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
-  </si>
-  <si>
-    <t>Ульянов</t>
   </si>
   <si>
     <t>/md_person/Ульянин_Николай_Васильевич.md</t>
@@ -1719,9 +1716,6 @@
       <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>357</v>
-      </c>
       <c r="E5" s="2"/>
       <c r="G5" s="4" t="s">
         <v>52</v>
@@ -1736,7 +1730,7 @@
         <v>53</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O5" t="s">
         <v>54</v>
@@ -2347,7 +2341,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N22"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F9">
       <formula1>$A:$A</formula1>
     </dataValidation>

--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="363">
   <si>
     <t>idA</t>
   </si>
@@ -1101,10 +1101,25 @@
     <t>число детей:</t>
   </si>
   <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
-  </si>
-  <si>
-    <t>/md_person/Ульянин_Николай_Васильевич.md</t>
+    <t>https://m-gorki.livejournal.com/9204.html</t>
+  </si>
+  <si>
+    <t>id_item</t>
+  </si>
+  <si>
+    <t>вещи</t>
+  </si>
+  <si>
+    <t>календарь</t>
+  </si>
+  <si>
+    <t>музей</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md ; https://bpmbpm.github.io/family-tree/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
+  </si>
+  <si>
+    <t>//md_person/Ульянин_Николай_Васильевич.md</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1618,7 @@
         <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -1730,7 +1745,7 @@
         <v>53</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O5" t="s">
         <v>54</v>
@@ -4287,17 +4302,26 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>156</v>
@@ -4337,6 +4361,34 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
+        <v>календарь-вещи.png</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="7" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -1119,7 +1119,7 @@
     <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md ; https://bpmbpm.github.io/family-tree/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
   </si>
   <si>
-    <t>//md_person/Ульянин_Николай_Васильевич.md</t>
+    <t>./md_person/Ульянин_Николай_Васильевич.md</t>
   </si>
 </sst>
 </file>

--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -1119,7 +1119,7 @@
     <t>https://ru.wikipedia.org/wiki/%D0%9B%D0%B5%D0%BD%D0%B8%D0%BD,_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87 ; https://www.wikidata.org/wiki/Q1394 ; https://github.com/bpmbpm/family-tree/blob/main/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md ; https://bpmbpm.github.io/family-tree/ver5/md_person/%D0%A3%D0%BB%D1%8C%D1%8F%D0%BD%D0%BE%D0%B2_%D0%92%D0%BB%D0%B0%D0%B4%D0%B8%D0%BC%D0%B8%D1%80_%D0%98%D0%BB%D1%8C%D0%B8%D1%87.md</t>
   </si>
   <si>
-    <t>./md_person/Ульянин_Николай_Васильевич.md</t>
+    <t>./md_person/Ульянин_Николай_Васильевич.md ; ./md_person/Ульянин_Николай_Васильевич.pdf</t>
   </si>
 </sst>
 </file>

--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -9,19 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="6195"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="6195" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
     <sheet name="family" sheetId="2" r:id="rId2"/>
-    <sheet name="foto_person" sheetId="3" r:id="rId3"/>
-    <sheet name="foto_family" sheetId="4" r:id="rId4"/>
-    <sheet name="foto_group" sheetId="5" r:id="rId5"/>
-    <sheet name="foto_location" sheetId="6" r:id="rId6"/>
-    <sheet name="foto_item" sheetId="10" r:id="rId7"/>
-    <sheet name="event" sheetId="7" r:id="rId8"/>
-    <sheet name="language" sheetId="8" r:id="rId9"/>
-    <sheet name="help" sheetId="9" r:id="rId10"/>
+    <sheet name="event" sheetId="7" r:id="rId3"/>
+    <sheet name="foto_person" sheetId="3" r:id="rId4"/>
+    <sheet name="foto_family" sheetId="4" r:id="rId5"/>
+    <sheet name="foto_event" sheetId="11" r:id="rId6"/>
+    <sheet name="foto_group" sheetId="5" r:id="rId7"/>
+    <sheet name="foto_location" sheetId="6" r:id="rId8"/>
+    <sheet name="foto_item" sheetId="10" r:id="rId9"/>
+    <sheet name="language" sheetId="8" r:id="rId10"/>
+    <sheet name="help" sheetId="9" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$22</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="365">
   <si>
     <t>idA</t>
   </si>
@@ -1120,6 +1121,12 @@
   </si>
   <si>
     <t>./md_person/Ульянин_Николай_Васильевич.md ; ./md_person/Ульянин_Николай_Васильевич.pdf</t>
+  </si>
+  <si>
+    <t>foto_item</t>
+  </si>
+  <si>
+    <t>foto_event</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1223,6 +1230,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2371,6 +2379,847 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" t="s">
+        <v>235</v>
+      </c>
+      <c r="E18" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B21" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>214</v>
+      </c>
+      <c r="B24" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>231</v>
+      </c>
+      <c r="E24" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>231</v>
+      </c>
+      <c r="E29" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>214</v>
+      </c>
+      <c r="B30" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" t="s">
+        <v>237</v>
+      </c>
+      <c r="E31" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E35" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" t="s">
+        <v>197</v>
+      </c>
+      <c r="C37" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" t="s">
+        <v>198</v>
+      </c>
+      <c r="C38" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" t="s">
+        <v>245</v>
+      </c>
+      <c r="E41" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>247</v>
+      </c>
+      <c r="E42" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>214</v>
+      </c>
+      <c r="B43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E44" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" t="s">
+        <v>252</v>
+      </c>
+      <c r="E45" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B46" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" t="s">
+        <v>254</v>
+      </c>
+      <c r="E46" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3538,7 +4387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.42578125" style="7" customWidth="1"/>
@@ -3551,7 +4400,7 @@
     <col min="9" max="9" width="13.140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3579,17 +4428,18 @@
       <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>B2&amp;"__"&amp;C2</f>
         <v>Ульянов_Илья_Николаевич__Бланк_Мария_Александровна</v>
@@ -3610,7 +4460,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="str">
         <f t="shared" ref="A3:A6" si="0">B3&amp;"__"&amp;C3</f>
         <v>Бланк_Александр_Дмитриевич__Гроссшопф_Анна_Ивановна</v>
@@ -3631,7 +4481,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Ульянов_Владимир_Ильич__Крупская_Надежда_Константиновна</v>
@@ -3655,7 +4505,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Ульянин_Николай_Васильевич__Смирнова_Анна_Алексеевна</v>
@@ -3679,7 +4529,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>Бланк_Александр_Дмитриевич__Эссен_Екатерина_Ивановна</v>
@@ -3709,6 +4559,185 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" style="7" customWidth="1"/>
+    <col min="12" max="13" width="16" style="7" customWidth="1"/>
+    <col min="14" max="14" width="26.140625" style="7" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K2" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="M3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3859,9 +4888,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.140625" style="7" customWidth="1"/>
@@ -3879,7 +4908,7 @@
     <col min="14" max="14" width="17" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
@@ -3922,8 +4951,11 @@
       <c r="N1" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>350</v>
       </c>
@@ -3956,47 +4988,47 @@
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E7" s="5"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.25">
@@ -4017,9 +5049,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <f>A2&amp;"-"&amp;B2&amp;"."&amp;C2</f>
+        <v>календарь-вещи.png</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="7" customWidth="1"/>
@@ -4033,7 +5161,7 @@
     <col min="10" max="10" width="32.85546875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>155</v>
       </c>
@@ -4067,8 +5195,11 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -4101,7 +5232,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>180</v>
       </c>
@@ -4134,43 +5265,43 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.25">
@@ -4197,9 +5328,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" style="7" customWidth="1"/>
@@ -4216,7 +5347,7 @@
     <col min="14" max="14" width="14.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>185</v>
       </c>
@@ -4259,8 +5390,11 @@
       <c r="N1" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>189</v>
       </c>
@@ -4300,9 +5434,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -4319,7 +5453,7 @@
     <col min="13" max="13" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>357</v>
       </c>
@@ -4362,8 +5496,11 @@
       <c r="N1" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>359</v>
       </c>
@@ -4394,1017 +5531,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="43.42578125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="7" customWidth="1"/>
-    <col min="12" max="13" width="16" style="7" customWidth="1"/>
-    <col min="14" max="14" width="26.140625" style="7" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I2" t="s">
-        <v>202</v>
-      </c>
-      <c r="K2" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="M3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.7109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="7" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>222</v>
-      </c>
-      <c r="E5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>224</v>
-      </c>
-      <c r="E6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>231</v>
-      </c>
-      <c r="E9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B10" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>224</v>
-      </c>
-      <c r="E10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>214</v>
-      </c>
-      <c r="B11" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" t="s">
-        <v>159</v>
-      </c>
-      <c r="D12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" t="s">
-        <v>235</v>
-      </c>
-      <c r="E13" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>214</v>
-      </c>
-      <c r="B14" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>231</v>
-      </c>
-      <c r="E14" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" t="s">
-        <v>233</v>
-      </c>
-      <c r="E16" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B17" t="s">
-        <v>197</v>
-      </c>
-      <c r="C17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E17" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" t="s">
-        <v>197</v>
-      </c>
-      <c r="C18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" t="s">
-        <v>235</v>
-      </c>
-      <c r="E18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>231</v>
-      </c>
-      <c r="E19" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B20" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" t="s">
-        <v>224</v>
-      </c>
-      <c r="E20" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B21" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>214</v>
-      </c>
-      <c r="B22" t="s">
-        <v>198</v>
-      </c>
-      <c r="C22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" t="s">
-        <v>229</v>
-      </c>
-      <c r="E22" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>214</v>
-      </c>
-      <c r="B23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" t="s">
-        <v>235</v>
-      </c>
-      <c r="E23" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>214</v>
-      </c>
-      <c r="B24" t="s">
-        <v>198</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
-        <v>231</v>
-      </c>
-      <c r="E24" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>214</v>
-      </c>
-      <c r="B25" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="s">
-        <v>224</v>
-      </c>
-      <c r="E25" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>214</v>
-      </c>
-      <c r="B26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>214</v>
-      </c>
-      <c r="B27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" t="s">
-        <v>159</v>
-      </c>
-      <c r="D27" t="s">
-        <v>229</v>
-      </c>
-      <c r="E27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>214</v>
-      </c>
-      <c r="B28" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D28" t="s">
-        <v>235</v>
-      </c>
-      <c r="E28" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>214</v>
-      </c>
-      <c r="B29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>231</v>
-      </c>
-      <c r="E29" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>214</v>
-      </c>
-      <c r="B30" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>214</v>
-      </c>
-      <c r="B31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" t="s">
-        <v>237</v>
-      </c>
-      <c r="E31" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>214</v>
-      </c>
-      <c r="B32" t="s">
-        <v>239</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D32" t="s">
-        <v>233</v>
-      </c>
-      <c r="E32" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>214</v>
-      </c>
-      <c r="B33" t="s">
-        <v>239</v>
-      </c>
-      <c r="C33" t="s">
-        <v>159</v>
-      </c>
-      <c r="D33" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>214</v>
-      </c>
-      <c r="B34" t="s">
-        <v>239</v>
-      </c>
-      <c r="C34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" t="s">
-        <v>235</v>
-      </c>
-      <c r="E34" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>214</v>
-      </c>
-      <c r="B35" t="s">
-        <v>239</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" t="s">
-        <v>231</v>
-      </c>
-      <c r="E35" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>214</v>
-      </c>
-      <c r="B36" t="s">
-        <v>239</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" t="s">
-        <v>224</v>
-      </c>
-      <c r="E36" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>214</v>
-      </c>
-      <c r="B37" t="s">
-        <v>197</v>
-      </c>
-      <c r="C37" t="s">
-        <v>166</v>
-      </c>
-      <c r="D37" t="s">
-        <v>240</v>
-      </c>
-      <c r="E37" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>214</v>
-      </c>
-      <c r="B38" t="s">
-        <v>198</v>
-      </c>
-      <c r="C38" t="s">
-        <v>166</v>
-      </c>
-      <c r="D38" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>241</v>
-      </c>
-      <c r="E39" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>214</v>
-      </c>
-      <c r="B40" t="s">
-        <v>215</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>243</v>
-      </c>
-      <c r="E40" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" t="s">
-        <v>215</v>
-      </c>
-      <c r="C41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" t="s">
-        <v>245</v>
-      </c>
-      <c r="E41" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>214</v>
-      </c>
-      <c r="B42" t="s">
-        <v>215</v>
-      </c>
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" t="s">
-        <v>247</v>
-      </c>
-      <c r="E42" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>214</v>
-      </c>
-      <c r="B43" t="s">
-        <v>226</v>
-      </c>
-      <c r="C43" t="s">
-        <v>141</v>
-      </c>
-      <c r="D43" t="s">
-        <v>355</v>
-      </c>
-      <c r="E43" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>214</v>
-      </c>
-      <c r="B44" t="s">
-        <v>226</v>
-      </c>
-      <c r="C44" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" t="s">
-        <v>250</v>
-      </c>
-      <c r="E44" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B45" t="s">
-        <v>215</v>
-      </c>
-      <c r="C45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" t="s">
-        <v>252</v>
-      </c>
-      <c r="E45" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B46" t="s">
-        <v>226</v>
-      </c>
-      <c r="C46" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" t="s">
-        <v>254</v>
-      </c>
-      <c r="E46" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
 </file>
--- a/ver5/tree.xlsx
+++ b/ver5/tree.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="6195" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26670" windowHeight="6195" firstSheet="1" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="foto_item" sheetId="10" r:id="rId9"/>
     <sheet name="language" sheetId="8" r:id="rId10"/>
     <sheet name="help" sheetId="9" r:id="rId11"/>
+    <sheet name="version" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">person!$A$1:$N$22</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="368">
   <si>
     <t>idA</t>
   </si>
@@ -1127,6 +1128,15 @@
   </si>
   <si>
     <t>foto_event</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>v_0.01</t>
   </si>
 </sst>
 </file>
@@ -3225,6 +3235,7 @@
   <cols>
     <col min="1" max="2" width="20" style="7" customWidth="1"/>
     <col min="3" max="3" width="60" style="7" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4382,6 +4393,34 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
